--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119796373</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,960 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126017426</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92546</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>848267</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7370721</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126017425</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>848215</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370738</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126017423</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>848210</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370646</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126017408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98332</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>848299</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370622</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126017415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82780</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>848321</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370732</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126017411</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>848300</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370726</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126017369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>848207</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370655</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126017368</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>848240</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370662</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126017403</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>848287</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7370645</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92546</v>
+        <v>92554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126017425</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R5" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R6" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1213,7 @@
         <v>126017415</v>
       </c>
       <c r="B7" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>126017411</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126017369</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R5" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R6" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R5" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R6" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126017425</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R5" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R6" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1213,7 @@
         <v>126017415</v>
       </c>
       <c r="B7" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>126017411</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126017369</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92562</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R5" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R6" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R5" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R6" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92564</v>
+        <v>92568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126017425</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126017423</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126017415</v>
       </c>
       <c r="B7" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>126017411</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126017369</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92568</v>
+        <v>92571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126017425</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126017423</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>126017408</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126017415</v>
       </c>
       <c r="B7" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>126017411</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126017369</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017423</v>
+        <v>126017408</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848210</v>
+        <v>848299</v>
       </c>
       <c r="R5" t="n">
-        <v>7370646</v>
+        <v>7370622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017408</v>
+        <v>126017423</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848299</v>
+        <v>848210</v>
       </c>
       <c r="R6" t="n">
-        <v>7370622</v>
+        <v>7370646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796373</v>
+        <v>126017415</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>848213</v>
+        <v>848321</v>
       </c>
       <c r="R2" t="n">
-        <v>7370650</v>
+        <v>7370732</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,7 +784,7 @@
         <v>126017426</v>
       </c>
       <c r="B3" t="n">
-        <v>92571</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017425</v>
+        <v>126017411</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>848215</v>
+        <v>848300</v>
       </c>
       <c r="R4" t="n">
-        <v>7370738</v>
+        <v>7370726</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017423</v>
+        <v>126017425</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>848210</v>
+        <v>848215</v>
       </c>
       <c r="R5" t="n">
-        <v>7370646</v>
+        <v>7370738</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017408</v>
+        <v>119796373</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>848299</v>
+        <v>848213</v>
       </c>
       <c r="R6" t="n">
-        <v>7370622</v>
+        <v>7370650</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126017415</v>
+        <v>126017369</v>
       </c>
       <c r="B7" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>848321</v>
+        <v>848207</v>
       </c>
       <c r="R7" t="n">
-        <v>7370732</v>
+        <v>7370655</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126017411</v>
+        <v>126017423</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>848300</v>
+        <v>848210</v>
       </c>
       <c r="R8" t="n">
-        <v>7370726</v>
+        <v>7370646</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126017369</v>
+        <v>126017408</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>848207</v>
+        <v>848299</v>
       </c>
       <c r="R9" t="n">
-        <v>7370655</v>
+        <v>7370622</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1531,7 +1526,7 @@
         <v>126017368</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1632,7 @@
         <v>126017403</v>
       </c>
       <c r="B11" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,6 +1732,112 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126017429</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>848341</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370647</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37997-2024 artfynd.xlsx
+++ b/artfynd/A 37997-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017415</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796373</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017408</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017368</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017403</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,8 +1893,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>